--- a/output/pdf_financials_xlsx/ORGN.xlsx
+++ b/output/pdf_financials_xlsx/ORGN.xlsx
@@ -1933,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>0</v>
+        <v>-0.000893</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.003193</v>
       </c>
     </row>
     <row r="92">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.7267439999999999</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.916279</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.953264</v>
       </c>
     </row>
     <row r="93">
@@ -2988,7 +2988,11 @@
           <t>Share-based payment reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.7267439999999999</v>
       </c>
@@ -3015,7 +3019,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ORGN.xlsx
+++ b/output/pdf_financials_xlsx/ORGN.xlsx
@@ -609,10 +609,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.193511</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.046227</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.859465</v>
+        <v>-3.052976</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.166842</v>
+        <v>-3.213069</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.720975</v>
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.859465</v>
+        <v>-3.052976</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.166842</v>
+        <v>-3.213069</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.720975</v>
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.473058</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.183277</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.088991</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.473058</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.183277</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.088991</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.5983540000000001</v>
+        <v>0.125296</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.261183</v>
+        <v>0.077906</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.9652230000000001</v>
+        <v>0.876232</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -2868,7 +2868,11 @@
           <t>Reclamation deposits (Note 6)</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n">
         <v>0.0635</v>
       </c>
@@ -3604,7 +3608,11 @@
           <t>Release of reclamation deposit</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -4963,7 +4971,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">

--- a/output/pdf_financials_xlsx/ORGN.xlsx
+++ b/output/pdf_financials_xlsx/ORGN.xlsx
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.345</v>
+        <v>-0.345</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.367354</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.106353</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.215413</v>
       </c>
     </row>
     <row r="116">
@@ -3674,7 +3674,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>0.367354</v>
       </c>
@@ -5510,7 +5514,11 @@
           <t>Income tax recovery (Note 13)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.345</v>
       </c>
